--- a/crawler/headpagepb.xlsx
+++ b/crawler/headpagepb.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA376"/>
+  <dimension ref="A1:AA399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.625" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -32248,88 +32248,2043 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="inlineStr">
+      <c r="A376" s="2" t="inlineStr">
         <is>
           <t>2026/6/29</t>
         </is>
       </c>
-      <c r="B376" t="n">
+      <c r="B376" s="2" t="n">
         <v>3.11</v>
       </c>
-      <c r="C376" t="n">
+      <c r="C376" s="2" t="n">
         <v>7.16</v>
       </c>
-      <c r="D376" t="n">
+      <c r="D376" s="2" t="n">
         <v>3.25</v>
       </c>
-      <c r="E376" t="n">
+      <c r="E376" s="2" t="n">
         <v>4.25</v>
       </c>
-      <c r="F376" t="n">
+      <c r="F376" s="2" t="n">
         <v>8.19</v>
       </c>
-      <c r="G376" t="n">
+      <c r="G376" s="2" t="n">
         <v>1.94</v>
       </c>
-      <c r="H376" t="n">
+      <c r="H376" s="2" t="n">
         <v>5.7</v>
       </c>
-      <c r="I376" t="n">
+      <c r="I376" s="2" t="n">
         <v>3.73</v>
       </c>
-      <c r="J376" t="n">
+      <c r="J376" s="2" t="n">
         <v>3.85</v>
       </c>
-      <c r="K376" t="n">
+      <c r="K376" s="2" t="n">
         <v>5.08</v>
       </c>
-      <c r="L376" t="n">
+      <c r="L376" s="2" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="M376" t="n">
+      <c r="M376" s="2" t="n">
         <v>3.29</v>
       </c>
-      <c r="N376" t="n">
+      <c r="N376" s="2" t="n">
         <v>2.81</v>
       </c>
-      <c r="O376" t="n">
+      <c r="O376" s="2" t="n">
         <v>8.32</v>
       </c>
-      <c r="P376" t="n">
+      <c r="P376" s="2" t="n">
         <v>5.13</v>
       </c>
-      <c r="Q376" t="n">
+      <c r="Q376" s="2" t="n">
         <v>1.7</v>
       </c>
-      <c r="R376" t="n">
+      <c r="R376" s="2" t="n">
         <v>2.72</v>
       </c>
-      <c r="S376" t="n">
+      <c r="S376" s="2" t="n">
         <v>1.89</v>
       </c>
-      <c r="T376" t="n">
+      <c r="T376" s="2" t="n">
         <v>15.12</v>
       </c>
-      <c r="U376" t="n">
+      <c r="U376" s="2" t="n">
         <v>3.1</v>
       </c>
-      <c r="V376" t="n">
+      <c r="V376" s="2" t="n">
         <v>3.91</v>
       </c>
-      <c r="W376" t="n">
+      <c r="W376" s="2" t="n">
         <v>1.59</v>
       </c>
-      <c r="X376" t="n">
+      <c r="X376" s="2" t="n">
         <v>2.51</v>
       </c>
-      <c r="Y376" t="n">
+      <c r="Y376" s="2" t="n">
         <v>8.640000000000001</v>
       </c>
-      <c r="Z376" t="n">
+      <c r="Z376" s="2" t="n">
         <v>0.78</v>
       </c>
-      <c r="AA376" t="n">
+      <c r="AA376" s="2" t="n">
         <v>0.82</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>2026/6/30</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="C377" s="2" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="D377" s="2" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="E377" s="2" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="F377" s="2" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="G377" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H377" s="2" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="I377" s="2" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="J377" s="2" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="K377" s="2" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="L377" s="2" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="M377" s="2" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N377" s="2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="O377" s="2" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="P377" s="2" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="Q377" s="2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R377" s="2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="S377" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T377" s="2" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="U377" s="2" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="V377" s="2" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="W377" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X377" s="2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Y377" s="2" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="Z377" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AA377" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/01</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="C378" s="2" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="D378" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E378" s="2" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="F378" s="2" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="G378" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H378" s="2" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="I378" s="2" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="J378" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="K378" s="2" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="L378" s="2" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="M378" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N378" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O378" s="2" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="P378" s="2" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="Q378" s="2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R378" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="S378" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T378" s="2" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="U378" s="2" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V378" s="2" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="W378" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X378" s="2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Y378" s="2" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="Z378" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AA378" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/02</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="C379" s="2" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="D379" s="2" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="E379" s="2" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="F379" s="2" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="G379" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H379" s="2" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="I379" s="2" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="J379" s="2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K379" s="2" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="L379" s="2" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="M379" s="2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N379" s="2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O379" s="2" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="P379" s="2" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="Q379" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R379" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S379" s="2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="T379" s="2" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="U379" s="2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V379" s="2" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="W379" s="2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X379" s="2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Y379" s="2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z379" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AA379" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/03</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="C380" s="2" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="D380" s="2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="E380" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F380" s="2" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="G380" s="2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H380" s="2" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="I380" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J380" s="2" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="K380" s="2" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="L380" s="2" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="M380" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N380" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O380" s="2" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="P380" s="2" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="Q380" s="2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R380" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S380" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T380" s="2" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="U380" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="V380" s="2" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="W380" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X380" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y380" s="2" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="Z380" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AA380" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/06</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="C381" s="2" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="D381" s="2" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="E381" s="2" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="F381" s="2" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="G381" s="2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H381" s="2" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="I381" s="2" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="J381" s="2" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="K381" s="2" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="L381" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="M381" s="2" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N381" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O381" s="2" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="P381" s="2" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="Q381" s="2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R381" s="2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="S381" s="2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="T381" s="2" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="U381" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="V381" s="2" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="W381" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X381" s="2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Y381" s="2" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="Z381" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AA381" s="2" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/07</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="C382" s="2" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="D382" s="2" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="E382" s="2" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="F382" s="2" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="G382" s="2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H382" s="2" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="I382" s="2" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="J382" s="2" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="K382" s="2" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="L382" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="M382" s="2" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N382" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O382" s="2" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="P382" s="2" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="Q382" s="2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R382" s="2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="S382" s="2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T382" s="2" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="U382" s="2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V382" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W382" s="2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X382" s="2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Y382" s="2" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="Z382" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AA382" s="2" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/08</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="C383" s="2" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="D383" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E383" s="2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="F383" s="2" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="G383" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H383" s="2" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="I383" s="2" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="J383" s="2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K383" s="2" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="L383" s="2" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="M383" s="2" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="N383" s="2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O383" s="2" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="P383" s="2" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="Q383" s="2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R383" s="2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="S383" s="2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="T383" s="2" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="U383" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="V383" s="2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="W383" s="2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X383" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y383" s="2" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="Z383" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AA383" s="2" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/09</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="C384" s="2" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="D384" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="E384" s="2" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="F384" s="2" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="G384" s="2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H384" s="2" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="I384" s="2" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="J384" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K384" s="2" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="L384" s="2" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="M384" s="2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N384" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O384" s="2" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="P384" s="2" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="Q384" s="2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R384" s="2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S384" s="2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="T384" s="2" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="U384" s="2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V384" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W384" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X384" s="2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y384" s="2" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="Z384" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AA384" s="2" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/10</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="C385" s="2" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="D385" s="2" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="E385" s="2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="F385" s="2" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="G385" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H385" s="2" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="I385" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J385" s="2" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="K385" s="2" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="L385" s="2" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="M385" s="2" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="N385" s="2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="O385" s="2" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="P385" s="2" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="Q385" s="2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R385" s="2" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="S385" s="2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T385" s="2" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="U385" s="2" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V385" s="2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="W385" s="2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X385" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y385" s="2" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="Z385" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AA385" s="2" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/13</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="C386" s="2" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D386" s="2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="E386" s="2" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="F386" s="2" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="G386" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H386" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I386" s="2" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="J386" s="2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="K386" s="2" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="L386" s="2" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="M386" s="2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N386" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O386" s="2" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="P386" s="2" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="Q386" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R386" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S386" s="2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="T386" s="2" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="U386" s="2" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="V386" s="2" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="W386" s="2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X386" s="2" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y386" s="2" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="Z386" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AA386" s="2" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/14</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="C387" s="2" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D387" s="2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="E387" s="2" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="F387" s="2" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="G387" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H387" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I387" s="2" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="J387" s="2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="K387" s="2" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="L387" s="2" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="M387" s="2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N387" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O387" s="2" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="P387" s="2" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="Q387" s="2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R387" s="2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="S387" s="2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="T387" s="2" t="n">
+        <v>13.87</v>
+      </c>
+      <c r="U387" s="2" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="V387" s="2" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="W387" s="2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X387" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y387" s="2" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="Z387" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AA387" s="2" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/15</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C388" s="2" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="D388" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="E388" s="2" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="F388" s="2" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="G388" s="2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H388" s="2" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="I388" s="2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J388" s="2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K388" s="2" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="L388" s="2" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="M388" s="2" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N388" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O388" s="2" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="P388" s="2" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="Q388" s="2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R388" s="2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="S388" s="2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T388" s="2" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="U388" s="2" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="V388" s="2" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="W388" s="2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X388" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y388" s="2" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="Z388" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AA388" s="2" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/16</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="C389" s="2" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="D389" s="2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="E389" s="2" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="F389" s="2" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="G389" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H389" s="2" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="I389" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="J389" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="K389" s="2" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="L389" s="2" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="M389" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N389" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="O389" s="2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="P389" s="2" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="Q389" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R389" s="2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="S389" s="2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T389" s="2" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="U389" s="2" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="V389" s="2" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="W389" s="2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X389" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y389" s="2" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="Z389" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AA389" s="2" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/17</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="C390" s="2" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="D390" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E390" s="2" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="F390" s="2" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="G390" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H390" s="2" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="I390" s="2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J390" s="2" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="K390" s="2" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="L390" s="2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M390" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N390" s="2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="O390" s="2" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="P390" s="2" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="Q390" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R390" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S390" s="2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="T390" s="2" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="U390" s="2" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="V390" s="2" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="W390" s="2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X390" s="2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y390" s="2" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="Z390" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AA390" s="2" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/20</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="C391" s="2" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="D391" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E391" s="2" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="F391" s="2" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="G391" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H391" s="2" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="I391" s="2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J391" s="2" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="K391" s="2" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="L391" s="2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M391" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N391" s="2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="O391" s="2" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="P391" s="2" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="Q391" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R391" s="2" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S391" s="2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="T391" s="2" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="U391" s="2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V391" s="2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="W391" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X391" s="2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y391" s="2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Z391" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA391" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/21</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="C392" s="2" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="D392" s="2" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="E392" s="2" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="F392" s="2" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="G392" s="2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H392" s="2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="I392" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J392" s="2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="K392" s="2" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="L392" s="2" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="M392" s="2" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N392" s="2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="O392" s="2" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="P392" s="2" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="Q392" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R392" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S392" s="2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="T392" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="U392" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="V392" s="2" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="W392" s="2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X392" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y392" s="2" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="Z392" s="2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AA392" s="2" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/22</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C393" s="2" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="D393" s="2" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="E393" s="2" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="F393" s="2" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G393" s="2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H393" s="2" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="I393" s="2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J393" s="2" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="K393" s="2" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="L393" s="2" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="M393" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="N393" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O393" s="2" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="P393" s="2" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="Q393" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R393" s="2" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="S393" s="2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T393" s="2" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="U393" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V393" s="2" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="W393" s="2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X393" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y393" s="2" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="Z393" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA393" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/23</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C394" s="2" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="D394" s="2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E394" s="2" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="F394" s="2" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="G394" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H394" s="2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I394" s="2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J394" s="2" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="K394" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L394" s="2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M394" s="2" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N394" s="2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O394" s="2" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="P394" s="2" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="Q394" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R394" s="2" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S394" s="2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="T394" s="2" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="U394" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V394" s="2" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="W394" s="2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X394" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y394" s="2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z394" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA394" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/24</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C395" s="2" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="D395" s="2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="E395" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F395" s="2" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="G395" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H395" s="2" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="I395" s="2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J395" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="K395" s="2" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="L395" s="2" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="M395" s="2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N395" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O395" s="2" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="P395" s="2" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="Q395" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R395" s="2" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S395" s="2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="T395" s="2" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="U395" s="2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="V395" s="2" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="W395" s="2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X395" s="2" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y395" s="2" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="Z395" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA395" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/27</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C396" s="2" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="D396" s="2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="E396" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F396" s="2" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="G396" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H396" s="2" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="I396" s="2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J396" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="K396" s="2" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="L396" s="2" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="M396" s="2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N396" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O396" s="2" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="P396" s="2" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="Q396" s="2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R396" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S396" s="2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T396" s="2" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="U396" s="2" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V396" s="2" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="W396" s="2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X396" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y396" s="2" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="Z396" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA396" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/28</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C397" s="2" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="D397" s="2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E397" s="2" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="F397" s="2" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="G397" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H397" s="2" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I397" s="2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="J397" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K397" s="2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L397" s="2" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="M397" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N397" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O397" s="2" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="P397" s="2" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="Q397" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R397" s="2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S397" s="2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="T397" s="2" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="U397" s="2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="V397" s="2" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="W397" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X397" s="2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y397" s="2" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="Z397" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA397" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/29</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="C398" s="2" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D398" s="2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="E398" s="2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="F398" s="2" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="G398" s="2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H398" s="2" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="I398" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J398" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K398" s="2" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="L398" s="2" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="M398" s="2" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N398" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O398" s="2" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="P398" s="2" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="Q398" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R398" s="2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S398" s="2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="T398" s="2" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="U398" s="2" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V398" s="2" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="W398" s="2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X398" s="2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y398" s="2" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="Z398" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AA398" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026/7/30</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="C399" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D399" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="E399" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="F399" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="G399" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H399" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="I399" t="n">
+        <v>3</v>
+      </c>
+      <c r="J399" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K399" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="L399" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="M399" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N399" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O399" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="P399" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="Q399" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R399" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S399" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="T399" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="U399" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V399" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="W399" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X399" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y399" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="Z399" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AA399" t="n">
+        <v>0.89</v>
       </c>
     </row>
   </sheetData>

--- a/crawler/headpagepb.xlsx
+++ b/crawler/headpagepb.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA399"/>
+  <dimension ref="A1:AA420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.625" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -34203,88 +34203,1873 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" t="inlineStr">
+      <c r="A399" s="2" t="inlineStr">
         <is>
           <t>2026/7/30</t>
         </is>
       </c>
-      <c r="B399" t="n">
+      <c r="B399" s="2" t="n">
         <v>2.73</v>
       </c>
-      <c r="C399" t="n">
+      <c r="C399" s="2" t="n">
         <v>5.75</v>
       </c>
-      <c r="D399" t="n">
+      <c r="D399" s="2" t="n">
         <v>2.95</v>
       </c>
-      <c r="E399" t="n">
+      <c r="E399" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="F399" t="n">
+      <c r="F399" s="2" t="n">
         <v>6.44</v>
       </c>
-      <c r="G399" t="n">
+      <c r="G399" s="2" t="n">
         <v>1.98</v>
       </c>
-      <c r="H399" t="n">
+      <c r="H399" s="2" t="n">
         <v>4.97</v>
       </c>
-      <c r="I399" t="n">
+      <c r="I399" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J399" t="n">
+      <c r="J399" s="2" t="n">
         <v>3.02</v>
       </c>
-      <c r="K399" t="n">
+      <c r="K399" s="2" t="n">
         <v>4.39</v>
       </c>
-      <c r="L399" t="n">
+      <c r="L399" s="2" t="n">
         <v>7.22</v>
       </c>
-      <c r="M399" t="n">
+      <c r="M399" s="2" t="n">
         <v>3.03</v>
       </c>
-      <c r="N399" t="n">
+      <c r="N399" s="2" t="n">
         <v>2.83</v>
       </c>
-      <c r="O399" t="n">
+      <c r="O399" s="2" t="n">
         <v>6.51</v>
       </c>
-      <c r="P399" t="n">
+      <c r="P399" s="2" t="n">
         <v>4.56</v>
       </c>
-      <c r="Q399" t="n">
+      <c r="Q399" s="2" t="n">
         <v>1.59</v>
       </c>
-      <c r="R399" t="n">
+      <c r="R399" s="2" t="n">
         <v>2.26</v>
       </c>
-      <c r="S399" t="n">
+      <c r="S399" s="2" t="n">
         <v>1.73</v>
       </c>
-      <c r="T399" t="n">
+      <c r="T399" s="2" t="n">
         <v>10.93</v>
       </c>
-      <c r="U399" t="n">
+      <c r="U399" s="2" t="n">
         <v>3.22</v>
       </c>
-      <c r="V399" t="n">
+      <c r="V399" s="2" t="n">
         <v>3.53</v>
       </c>
-      <c r="W399" t="n">
+      <c r="W399" s="2" t="n">
         <v>1.51</v>
       </c>
-      <c r="X399" t="n">
+      <c r="X399" s="2" t="n">
         <v>2.38</v>
       </c>
-      <c r="Y399" t="n">
+      <c r="Y399" s="2" t="n">
         <v>6.31</v>
       </c>
-      <c r="Z399" t="n">
+      <c r="Z399" s="2" t="n">
         <v>0.85</v>
       </c>
-      <c r="AA399" t="n">
+      <c r="AA399" s="2" t="n">
         <v>0.89</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>2026/7/31</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="C400" s="2" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="D400" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E400" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="F400" s="2" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="G400" s="2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H400" s="2" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I400" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="J400" s="2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="K400" s="2" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="L400" s="2" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="M400" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N400" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O400" s="2" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="P400" s="2" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="Q400" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R400" s="2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S400" s="2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="T400" s="2" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="U400" s="2" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V400" s="2" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="W400" s="2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X400" s="2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y400" s="2" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="Z400" s="2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AA400" s="2" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/03</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C401" s="2" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="D401" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E401" s="2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="F401" s="2" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="G401" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H401" s="2" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="I401" s="2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="J401" s="2" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="K401" s="2" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="L401" s="2" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="M401" s="2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N401" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O401" s="2" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="P401" s="2" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="Q401" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R401" s="2" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="S401" s="2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="T401" s="2" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="U401" s="2" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V401" s="2" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="W401" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X401" s="2" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y401" s="2" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="Z401" s="2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AA401" s="2" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/04</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="C402" s="2" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="D402" s="2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="E402" s="2" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="F402" s="2" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="G402" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H402" s="2" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="I402" s="2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="J402" s="2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K402" s="2" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="L402" s="2" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="M402" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N402" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O402" s="2" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="P402" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q402" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R402" s="2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S402" s="2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T402" s="2" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="U402" s="2" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="V402" s="2" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="W402" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X402" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y402" s="2" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="Z402" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AA402" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/05</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C403" s="2" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="D403" s="2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="E403" s="2" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="F403" s="2" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="G403" s="2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H403" s="2" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="I403" s="2" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="J403" s="2" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="K403" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L403" s="2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M403" s="2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N403" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O403" s="2" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="P403" s="2" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="Q403" s="2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R403" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S403" s="2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="T403" s="2" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="U403" s="2" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="V403" s="2" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="W403" s="2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X403" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y403" s="2" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="Z403" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA403" s="2" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/06</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C404" s="2" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="D404" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E404" s="2" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="F404" s="2" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="G404" s="2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H404" s="2" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="I404" s="2" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="J404" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K404" s="2" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="L404" s="2" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="M404" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N404" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O404" s="2" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="P404" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q404" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R404" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="S404" s="2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T404" s="2" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="U404" s="2" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="V404" s="2" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="W404" s="2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X404" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y404" s="2" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="Z404" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA404" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/07</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="C405" s="2" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="D405" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="E405" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F405" s="2" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="G405" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H405" s="2" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="I405" s="2" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="J405" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="K405" s="2" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="L405" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M405" s="2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N405" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O405" s="2" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="P405" s="2" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="Q405" s="2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R405" s="2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="S405" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T405" s="2" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="U405" s="2" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="V405" s="2" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="W405" s="2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X405" s="2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Y405" s="2" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="Z405" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA405" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/10</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="C406" s="2" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="D406" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="E406" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F406" s="2" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="G406" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H406" s="2" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="I406" s="2" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="J406" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="K406" s="2" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="L406" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M406" s="2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N406" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O406" s="2" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="P406" s="2" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="Q406" s="2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R406" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S406" s="2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T406" s="2" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="U406" s="2" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="V406" s="2" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="W406" s="2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X406" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y406" s="2" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="Z406" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AA406" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/11</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C407" s="2" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="D407" s="2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="E407" s="2" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="F407" s="2" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="G407" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H407" s="2" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="I407" s="2" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="J407" s="2" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="K407" s="2" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="L407" s="2" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="M407" s="2" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="N407" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O407" s="2" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="P407" s="2" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="Q407" s="2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R407" s="2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="S407" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T407" s="2" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="U407" s="2" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="V407" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W407" s="2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X407" s="2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Y407" s="2" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="Z407" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AA407" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/12</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C408" s="2" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="D408" s="2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="E408" s="2" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="F408" s="2" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="G408" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H408" s="2" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="I408" s="2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J408" s="2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="K408" s="2" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="L408" s="2" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="M408" s="2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N408" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O408" s="2" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="P408" s="2" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="Q408" s="2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R408" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S408" s="2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T408" s="2" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="U408" s="2" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="V408" s="2" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="W408" s="2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X408" s="2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Y408" s="2" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="Z408" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA408" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/13</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C409" s="2" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="D409" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="E409" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F409" s="2" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="G409" s="2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H409" s="2" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="I409" s="2" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="J409" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K409" s="2" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="L409" s="2" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="M409" s="2" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="N409" s="2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O409" s="2" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="P409" s="2" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="Q409" s="2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R409" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S409" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T409" s="2" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="U409" s="2" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="V409" s="2" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="W409" s="2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X409" s="2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y409" s="2" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="Z409" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA409" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/14</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="C410" s="2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D410" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="E410" s="2" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="F410" s="2" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="G410" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H410" s="2" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="I410" s="2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J410" s="2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="K410" s="2" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="L410" s="2" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="M410" s="2" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N410" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O410" s="2" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="P410" s="2" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="Q410" s="2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R410" s="2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="S410" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T410" s="2" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="U410" s="2" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="V410" s="2" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="W410" s="2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X410" s="2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y410" s="2" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="Z410" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA410" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/17</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="C411" s="2" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="D411" s="2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="E411" s="2" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="F411" s="2" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="G411" s="2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H411" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I411" s="2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="J411" s="2" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="K411" s="2" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="L411" s="2" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="M411" s="2" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="N411" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O411" s="2" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="P411" s="2" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="Q411" s="2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R411" s="2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S411" s="2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="T411" s="2" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="U411" s="2" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="V411" s="2" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="W411" s="2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X411" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y411" s="2" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="Z411" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA411" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/18</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C412" s="2" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="D412" s="2" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="E412" s="2" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="F412" s="2" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="G412" s="2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H412" s="2" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="I412" s="2" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="J412" s="2" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="K412" s="2" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="L412" s="2" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="M412" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N412" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O412" s="2" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="P412" s="2" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="Q412" s="2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R412" s="2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S412" s="2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="T412" s="2" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="U412" s="2" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="V412" s="2" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="W412" s="2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X412" s="2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Y412" s="2" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="Z412" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA412" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/19</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="C413" s="2" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="D413" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E413" s="2" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="F413" s="2" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="G413" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="I413" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="J413" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="K413" s="2" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="L413" s="2" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="M413" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O413" s="2" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="P413" s="2" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="Q413" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R413" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S413" s="2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="V413" s="2" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="W413" s="2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X413" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y413" s="2" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="Z413" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AA413" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/20</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C414" s="2" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="D414" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E414" s="2" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="F414" s="2" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="G414" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="I414" s="2" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="J414" s="2" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="K414" s="2" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="L414" s="2" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="M414" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O414" s="2" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="P414" s="2" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="Q414" s="2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R414" s="2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="S414" s="2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V414" s="2" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="W414" s="2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X414" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y414" s="2" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="Z414" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AA414" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/21</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C415" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D415" s="2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="E415" s="2" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="F415" s="2" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="G415" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H415" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I415" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="J415" s="2" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="K415" s="2" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="L415" s="2" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="M415" s="2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O415" s="2" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="P415" s="2" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="Q415" s="2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R415" s="2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="S415" s="2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="V415" s="2" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="W415" s="2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X415" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y415" s="2" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="Z415" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA415" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/24</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="C416" s="2" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="D416" s="2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E416" s="2" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="F416" s="2" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="G416" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H416" s="2" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="I416" s="2" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="J416" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="K416" s="2" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="L416" s="2" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="M416" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="N416" s="2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="O416" s="2" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="P416" s="2" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="Q416" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R416" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S416" s="2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="T416" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="U416" s="2" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="V416" s="2" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="W416" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X416" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y416" s="2" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="Z416" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AA416" s="2" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/25</t>
+        </is>
+      </c>
+      <c r="B417" s="2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="C417" s="2" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="D417" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E417" s="2" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="F417" s="2" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="G417" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H417" s="2" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="I417" s="2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="J417" s="2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K417" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L417" s="2" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="M417" s="2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N417" s="2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O417" s="2" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="P417" s="2" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="Q417" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R417" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S417" s="2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="T417" s="2" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="U417" s="2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V417" s="2" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="W417" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X417" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y417" s="2" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="Z417" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AA417" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/26</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C418" s="2" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D418" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E418" s="2" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="F418" s="2" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="G418" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H418" s="2" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="I418" s="2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="J418" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="K418" s="2" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="L418" s="2" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="M418" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N418" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O418" s="2" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="P418" s="2" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="Q418" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R418" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S418" s="2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="T418" s="2" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="U418" s="2" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="V418" s="2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="W418" s="2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X418" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y418" s="2" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="Z418" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AA418" s="2" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/27</t>
+        </is>
+      </c>
+      <c r="B419" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C419" s="2" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="D419" s="2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E419" s="2" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="F419" s="2" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="G419" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H419" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I419" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="J419" s="2" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="K419" s="2" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="L419" s="2" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="M419" s="2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N419" s="2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O419" s="2" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="P419" s="2" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="Q419" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R419" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S419" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T419" s="2" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="U419" s="2" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="V419" s="2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="W419" s="2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X419" s="2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Y419" s="2" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="Z419" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AA419" s="2" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026/8/28</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="C420" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="D420" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E420" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F420" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="G420" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H420" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="I420" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J420" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="K420" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="L420" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="M420" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N420" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O420" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="P420" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="Q420" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R420" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="S420" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="T420" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="U420" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V420" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="W420" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X420" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Y420" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="Z420" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA420" t="n">
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>

--- a/crawler/headpagepb.xlsx
+++ b/crawler/headpagepb.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA420"/>
+  <dimension ref="A1:AA441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.625" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -35988,88 +35988,1873 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" t="inlineStr">
+      <c r="A420" s="2" t="inlineStr">
         <is>
           <t>2026/8/28</t>
         </is>
       </c>
-      <c r="B420" t="n">
+      <c r="B420" s="2" t="n">
         <v>2.77</v>
       </c>
-      <c r="C420" t="n">
+      <c r="C420" s="2" t="n">
         <v>5.72</v>
       </c>
-      <c r="D420" t="n">
+      <c r="D420" s="2" t="n">
         <v>2.93</v>
       </c>
-      <c r="E420" t="n">
+      <c r="E420" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="F420" t="n">
+      <c r="F420" s="2" t="n">
         <v>6.25</v>
       </c>
-      <c r="G420" t="n">
+      <c r="G420" s="2" t="n">
         <v>1.95</v>
       </c>
-      <c r="H420" t="n">
+      <c r="H420" s="2" t="n">
         <v>4.85</v>
       </c>
-      <c r="I420" t="n">
+      <c r="I420" s="2" t="n">
         <v>3.25</v>
       </c>
-      <c r="J420" t="n">
+      <c r="J420" s="2" t="n">
         <v>3.39</v>
       </c>
-      <c r="K420" t="n">
+      <c r="K420" s="2" t="n">
         <v>4.29</v>
       </c>
-      <c r="L420" t="n">
+      <c r="L420" s="2" t="n">
         <v>7.08</v>
       </c>
-      <c r="M420" t="n">
+      <c r="M420" s="2" t="n">
         <v>2.95</v>
       </c>
-      <c r="N420" t="n">
+      <c r="N420" s="2" t="n">
         <v>2.78</v>
       </c>
-      <c r="O420" t="n">
+      <c r="O420" s="2" t="n">
         <v>6.32</v>
       </c>
-      <c r="P420" t="n">
+      <c r="P420" s="2" t="n">
         <v>4.43</v>
       </c>
-      <c r="Q420" t="n">
+      <c r="Q420" s="2" t="n">
         <v>1.61</v>
       </c>
-      <c r="R420" t="n">
+      <c r="R420" s="2" t="n">
         <v>2.47</v>
       </c>
-      <c r="S420" t="n">
+      <c r="S420" s="2" t="n">
         <v>1.79</v>
       </c>
-      <c r="T420" t="n">
+      <c r="T420" s="2" t="n">
         <v>9.91</v>
       </c>
-      <c r="U420" t="n">
+      <c r="U420" s="2" t="n">
         <v>3.42</v>
       </c>
-      <c r="V420" t="n">
+      <c r="V420" s="2" t="n">
         <v>3.42</v>
       </c>
-      <c r="W420" t="n">
+      <c r="W420" s="2" t="n">
         <v>1.52</v>
       </c>
-      <c r="X420" t="n">
+      <c r="X420" s="2" t="n">
         <v>2.44</v>
       </c>
-      <c r="Y420" t="n">
+      <c r="Y420" s="2" t="n">
         <v>6.79</v>
       </c>
-      <c r="Z420" t="n">
+      <c r="Z420" s="2" t="n">
         <v>0.84</v>
       </c>
-      <c r="AA420" t="n">
+      <c r="AA420" s="2" t="n">
         <v>0.9</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>2026/8/31</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C421" s="2" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="D421" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E421" s="2" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="F421" s="2" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="G421" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H421" s="2" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="I421" s="2" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="J421" s="2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="K421" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L421" s="2" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="M421" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="N421" s="2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="O421" s="2" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="P421" s="2" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="Q421" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R421" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S421" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T421" s="2" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="U421" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V421" s="2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="W421" s="2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X421" s="2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Y421" s="2" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="Z421" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA421" s="2" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/01</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="C422" s="2" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="D422" s="2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E422" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F422" s="2" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="G422" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H422" s="2" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="I422" s="2" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="J422" s="2" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="K422" s="2" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="L422" s="2" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="M422" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N422" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O422" s="2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="P422" s="2" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="Q422" s="2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R422" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S422" s="2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="T422" s="2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="U422" s="2" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="V422" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="W422" s="2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X422" s="2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y422" s="2" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="Z422" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AA422" s="2" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/02</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="C423" s="2" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="D423" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E423" s="2" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="F423" s="2" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="G423" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H423" s="2" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="I423" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="J423" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="K423" s="2" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="L423" s="2" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="M423" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N423" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O423" s="2" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="P423" s="2" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="Q423" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R423" s="2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S423" s="2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="T423" s="2" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="U423" s="2" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="V423" s="2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="W423" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X423" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y423" s="2" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="Z423" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA423" s="2" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/03</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="C424" s="2" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="D424" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E424" s="2" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="F424" s="2" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="G424" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H424" s="2" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="I424" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="J424" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K424" s="2" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="L424" s="2" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="M424" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N424" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O424" s="2" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="P424" s="2" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="Q424" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R424" s="2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="S424" s="2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="T424" s="2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="U424" s="2" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="V424" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="W424" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X424" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y424" s="2" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="Z424" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA424" s="2" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/04</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="C425" s="2" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="D425" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E425" s="2" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="F425" s="2" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="G425" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H425" s="2" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="I425" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="J425" s="2" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="K425" s="2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="L425" s="2" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="M425" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N425" s="2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O425" s="2" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="P425" s="2" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="Q425" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R425" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S425" s="2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="T425" s="2" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="U425" s="2" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="V425" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W425" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X425" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y425" s="2" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="Z425" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AA425" s="2" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/07</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="C426" s="2" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="D426" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E426" s="2" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="F426" s="2" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="G426" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H426" s="2" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="I426" s="2" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="J426" s="2" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="K426" s="2" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="L426" s="2" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="M426" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N426" s="2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O426" s="2" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="P426" s="2" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="Q426" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R426" s="2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="S426" s="2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="T426" s="2" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="U426" s="2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="V426" s="2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="W426" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X426" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y426" s="2" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="Z426" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA426" s="2" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/08</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="C427" s="2" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="D427" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E427" s="2" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="F427" s="2" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="G427" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H427" s="2" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="I427" s="2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J427" s="2" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="K427" s="2" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="L427" s="2" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="M427" s="2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="N427" s="2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="O427" s="2" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="P427" s="2" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="Q427" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R427" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S427" s="2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T427" s="2" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="U427" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V427" s="2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="W427" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X427" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y427" s="2" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="Z427" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA427" s="2" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/09</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="C428" s="2" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="D428" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E428" s="2" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="F428" s="2" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="G428" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H428" s="2" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="I428" s="2" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="J428" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K428" s="2" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="L428" s="2" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="M428" s="2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="N428" s="2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O428" s="2" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="P428" s="2" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Q428" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R428" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S428" s="2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T428" s="2" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="U428" s="2" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="V428" s="2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="W428" s="2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X428" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y428" s="2" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="Z428" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AA428" s="2" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/10</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="C429" s="2" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="D429" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E429" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F429" s="2" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="G429" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H429" s="2" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="I429" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J429" s="2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K429" s="2" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="L429" s="2" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="M429" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N429" s="2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="O429" s="2" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="P429" s="2" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="Q429" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R429" s="2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S429" s="2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="T429" s="2" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="U429" s="2" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="V429" s="2" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="W429" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X429" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y429" s="2" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="Z429" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AA429" s="2" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/11</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C430" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D430" s="2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E430" s="2" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F430" s="2" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="G430" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H430" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I430" s="2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="J430" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="K430" s="2" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="L430" s="2" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="M430" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N430" s="2" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O430" s="2" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="P430" s="2" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="Q430" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R430" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S430" s="2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T430" s="2" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="U430" s="2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V430" s="2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="W430" s="2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X430" s="2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y430" s="2" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="Z430" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA430" s="2" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/14</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="C431" s="2" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="D431" s="2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="E431" s="2" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="F431" s="2" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="G431" s="2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H431" s="2" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="I431" s="2" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="J431" s="2" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="K431" s="2" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="L431" s="2" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="M431" s="2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="N431" s="2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O431" s="2" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="P431" s="2" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="Q431" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R431" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="S431" s="2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T431" s="2" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="U431" s="2" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="V431" s="2" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="W431" s="2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X431" s="2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y431" s="2" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="Z431" s="2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AA431" s="2" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/15</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="C432" s="2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D432" s="2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E432" s="2" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="F432" s="2" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="G432" s="2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H432" s="2" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="I432" s="2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="J432" s="2" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="K432" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="L432" s="2" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="M432" s="2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N432" s="2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O432" s="2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="P432" s="2" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="Q432" s="2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R432" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S432" s="2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="T432" s="2" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="U432" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="V432" s="2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="W432" s="2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X432" s="2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y432" s="2" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="Z432" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AA432" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/16</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C433" s="2" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="D433" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E433" s="2" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="F433" s="2" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="G433" s="2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H433" s="2" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="I433" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="J433" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K433" s="2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="L433" s="2" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="M433" s="2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="N433" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O433" s="2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P433" s="2" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="Q433" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R433" s="2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S433" s="2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T433" s="2" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="U433" s="2" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="V433" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W433" s="2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X433" s="2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y433" s="2" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="Z433" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AA433" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/17</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="C434" s="2" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="D434" s="2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="E434" s="2" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="F434" s="2" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="G434" s="2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H434" s="2" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="I434" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="J434" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K434" s="2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="L434" s="2" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="M434" s="2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="N434" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O434" s="2" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="P434" s="2" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="Q434" s="2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R434" s="2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S434" s="2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T434" s="2" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="U434" s="2" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="V434" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W434" s="2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X434" s="2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y434" s="2" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="Z434" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AA434" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/18</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="C435" s="2" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="D435" s="2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="E435" s="2" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="F435" s="2" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="G435" s="2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H435" s="2" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="I435" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="J435" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K435" s="2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="L435" s="2" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="M435" s="2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="N435" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O435" s="2" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="P435" s="2" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="Q435" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R435" s="2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="S435" s="2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="T435" s="2" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="U435" s="2" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="V435" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W435" s="2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X435" s="2" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y435" s="2" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="Z435" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AA435" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/21</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="C436" s="2" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="D436" s="2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E436" s="2" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F436" s="2" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="G436" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H436" s="2" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="I436" s="2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J436" s="2" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="K436" s="2" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="L436" s="2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="M436" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N436" s="2" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="O436" s="2" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="P436" s="2" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="Q436" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R436" s="2" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="S436" s="2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T436" s="2" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="U436" s="2" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="V436" s="2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="W436" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X436" s="2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y436" s="2" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="Z436" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AA436" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/22</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="C437" s="2" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="D437" s="2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E437" s="2" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F437" s="2" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G437" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H437" s="2" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="I437" s="2" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="J437" s="2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K437" s="2" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="L437" s="2" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="M437" s="2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N437" s="2" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="O437" s="2" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="P437" s="2" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="Q437" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R437" s="2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="S437" s="2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T437" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="U437" s="2" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="V437" s="2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="W437" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X437" s="2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y437" s="2" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="Z437" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AA437" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/23</t>
+        </is>
+      </c>
+      <c r="B438" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C438" s="2" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="D438" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="E438" s="2" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="F438" s="2" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="G438" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H438" s="2" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="I438" s="2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J438" s="2" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="K438" s="2" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="L438" s="2" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="M438" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N438" s="2" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="O438" s="2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="P438" s="2" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q438" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R438" s="2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="S438" s="2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T438" s="2" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="U438" s="2" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="V438" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W438" s="2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X438" s="2" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y438" s="2" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="Z438" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AA438" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/24</t>
+        </is>
+      </c>
+      <c r="B439" s="2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="C439" s="2" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="D439" s="2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="E439" s="2" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="F439" s="2" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="G439" s="2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H439" s="2" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="I439" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="J439" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K439" s="2" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="L439" s="2" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="M439" s="2" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="N439" s="2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O439" s="2" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="P439" s="2" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="Q439" s="2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R439" s="2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="S439" s="2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T439" s="2" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="U439" s="2" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V439" s="2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W439" s="2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X439" s="2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y439" s="2" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="Z439" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AA439" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>2026/9/28</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="C440" s="2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D440" s="2" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E440" s="2" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="F440" s="2" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="G440" s="2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H440" s="2" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="I440" s="2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J440" s="2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K440" s="2" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="L440" s="2" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="M440" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N440" s="2" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="O440" s="2" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="P440" s="2" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="Q440" s="2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R440" s="2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S440" s="2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="T440" s="2" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="U440" s="2" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V440" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W440" s="2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X440" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y440" s="2" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="Z440" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AA440" s="2" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026/9/29</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="C441" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="D441" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E441" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="F441" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="G441" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H441" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="I441" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="J441" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="K441" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="L441" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="M441" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="N441" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="O441" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="P441" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R441" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S441" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="T441" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="U441" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="V441" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W441" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X441" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Y441" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="Z441" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AA441" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
